--- a/results_(stress_test)_PCCxSigmoid-PLI-/cnn_evaluation(stress_test)_k-heaviside_p-30_nm_basis-False_nm_modifier-False.xlsx
+++ b/results_(stress_test)_PCCxSigmoid-PLI-/cnn_evaluation(stress_test)_k-heaviside_p-30_nm_basis-False_nm_modifier-False.xlsx
@@ -10,6 +10,7 @@
     <sheet name="nrr_8" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="summary_t" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="nrr_4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1076,7 +1077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1139,6 +1140,44 @@
         <v>4.442945966320054</v>
       </c>
       <c r="E3" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>57.67625729172973</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56.89080946962518</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.965301038660109</v>
+      </c>
+      <c r="D4" t="n">
+        <v>57.67625729172973</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7.018507393632339</v>
+      </c>
+      <c r="B5" t="n">
+        <v>7.26938859393712</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.1468635160837836</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7.018507393632339</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>Std</t>
         </is>
@@ -1155,7 +1194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1226,6 +1265,681 @@
         <v>0.1294516996886194</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>57.67625729172973</v>
+      </c>
+      <c r="B3" t="n">
+        <v>7.018507393632339</v>
+      </c>
+      <c r="C3" t="n">
+        <v>56.89080946962518</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7.26938859393712</v>
+      </c>
+      <c r="E3" t="n">
+        <v>57.67625729172973</v>
+      </c>
+      <c r="F3" t="n">
+        <v>7.018507393632339</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.965301038660109</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.1468635160837836</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>f1_score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>55.44546233098902</v>
+      </c>
+      <c r="C2" t="n">
+        <v>53.94197856446974</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.043466028074423</v>
+      </c>
+      <c r="E2" t="n">
+        <v>55.44546233098902</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>56.98146177735102</v>
+      </c>
+      <c r="C3" t="n">
+        <v>56.48160070267024</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9449464271465938</v>
+      </c>
+      <c r="E3" t="n">
+        <v>56.98146177735102</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>58.0005882403827</v>
+      </c>
+      <c r="C4" t="n">
+        <v>57.39653083260077</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9813590804735821</v>
+      </c>
+      <c r="E4" t="n">
+        <v>58.0005882403827</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>52.2315071929688</v>
+      </c>
+      <c r="C5" t="n">
+        <v>50.79489904763322</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.021987103422483</v>
+      </c>
+      <c r="E5" t="n">
+        <v>52.2315071929688</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>53.01966279985121</v>
+      </c>
+      <c r="C6" t="n">
+        <v>51.82394072791119</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.056425074736277</v>
+      </c>
+      <c r="E6" t="n">
+        <v>53.01966279985121</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>49.98702410920509</v>
+      </c>
+      <c r="C7" t="n">
+        <v>49.37508534115851</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.119014509518941</v>
+      </c>
+      <c r="E7" t="n">
+        <v>49.9870241092051</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>65.93205823579788</v>
+      </c>
+      <c r="C8" t="n">
+        <v>65.0727870948522</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8128122910857201</v>
+      </c>
+      <c r="E8" t="n">
+        <v>65.93205823579788</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>62.3958684763709</v>
+      </c>
+      <c r="C9" t="n">
+        <v>61.51008841575501</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8708240449428558</v>
+      </c>
+      <c r="E9" t="n">
+        <v>62.3958684763709</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>63.80764539485635</v>
+      </c>
+      <c r="C10" t="n">
+        <v>63.18885751934488</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8069562842448553</v>
+      </c>
+      <c r="E10" t="n">
+        <v>63.80764539485635</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>53.61170944385331</v>
+      </c>
+      <c r="C11" t="n">
+        <v>51.91121612312944</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.049802621205648</v>
+      </c>
+      <c r="E11" t="n">
+        <v>53.61170944385331</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>50.13261360392391</v>
+      </c>
+      <c r="C12" t="n">
+        <v>48.70907436304621</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.147864644726118</v>
+      </c>
+      <c r="E12" t="n">
+        <v>50.13261360392391</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>58.57022984627895</v>
+      </c>
+      <c r="C13" t="n">
+        <v>58.43285074975923</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.9601865788300833</v>
+      </c>
+      <c r="E13" t="n">
+        <v>58.57022984627895</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>49.10777774894247</v>
+      </c>
+      <c r="C14" t="n">
+        <v>47.67723606544098</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.148986574014028</v>
+      </c>
+      <c r="E14" t="n">
+        <v>49.10777774894247</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>53.61292052699417</v>
+      </c>
+      <c r="C15" t="n">
+        <v>53.52249653259317</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.031795523564021</v>
+      </c>
+      <c r="E15" t="n">
+        <v>53.61292052699417</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>50.22422339293593</v>
+      </c>
+      <c r="C16" t="n">
+        <v>49.15763735596538</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.128277689218521</v>
+      </c>
+      <c r="E16" t="n">
+        <v>50.22422339293593</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>58.41858493585585</v>
+      </c>
+      <c r="C17" t="n">
+        <v>58.20367574936396</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.9265407443046569</v>
+      </c>
+      <c r="E17" t="n">
+        <v>58.41858493585585</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>60.42379259336153</v>
+      </c>
+      <c r="C18" t="n">
+        <v>59.99159383833019</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.8731925308704376</v>
+      </c>
+      <c r="E18" t="n">
+        <v>60.42379259336153</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>60.26799539788406</v>
+      </c>
+      <c r="C19" t="n">
+        <v>60.36593328522618</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.8781889547904334</v>
+      </c>
+      <c r="E19" t="n">
+        <v>60.26799539788406</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>55.30177596692013</v>
+      </c>
+      <c r="C20" t="n">
+        <v>54.77527981607945</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.9813975582520167</v>
+      </c>
+      <c r="E20" t="n">
+        <v>55.30177596692013</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>54.28740733051323</v>
+      </c>
+      <c r="C21" t="n">
+        <v>52.21838390568998</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.175802049040794</v>
+      </c>
+      <c r="E21" t="n">
+        <v>54.28740733051323</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>57.974376940977</v>
+      </c>
+      <c r="C22" t="n">
+        <v>57.58464291032495</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.9433234055836996</v>
+      </c>
+      <c r="E22" t="n">
+        <v>57.974376940977</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>53.7569529148176</v>
+      </c>
+      <c r="C23" t="n">
+        <v>53.21021642128669</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.065904729068279</v>
+      </c>
+      <c r="E23" t="n">
+        <v>53.7569529148176</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>50.6602998295833</v>
+      </c>
+      <c r="C24" t="n">
+        <v>49.87178948525333</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.11393061876297</v>
+      </c>
+      <c r="E24" t="n">
+        <v>50.6602998295833</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>52.42969229837628</v>
+      </c>
+      <c r="C25" t="n">
+        <v>52.1007239729199</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.012727775176366</v>
+      </c>
+      <c r="E25" t="n">
+        <v>52.42969229837628</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>63.87771520514883</v>
+      </c>
+      <c r="C26" t="n">
+        <v>62.92103970210128</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.8306486795345942</v>
+      </c>
+      <c r="E26" t="n">
+        <v>63.87771520514883</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>52.99794980925441</v>
+      </c>
+      <c r="C27" t="n">
+        <v>52.27371868643657</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.02181005179882</v>
+      </c>
+      <c r="E27" t="n">
+        <v>52.99794980925441</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>56.44702808847827</v>
+      </c>
+      <c r="C28" t="n">
+        <v>54.85467185105475</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.033196038007736</v>
+      </c>
+      <c r="E28" t="n">
+        <v>56.44702808847827</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>69.68148513395445</v>
+      </c>
+      <c r="C29" t="n">
+        <v>69.04886835783826</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.742389494801561</v>
+      </c>
+      <c r="E29" t="n">
+        <v>69.68148513395445</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>69.91314803761279</v>
+      </c>
+      <c r="C30" t="n">
+        <v>69.40456799392368</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.7364136228958766</v>
+      </c>
+      <c r="E30" t="n">
+        <v>69.91314803761279</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>80.78876114845283</v>
+      </c>
+      <c r="C31" t="n">
+        <v>80.90289867659584</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.498860431710879</v>
+      </c>
+      <c r="E31" t="n">
+        <v>80.78876114845283</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>57.67625729172973</v>
+      </c>
+      <c r="C32" t="n">
+        <v>56.89080946962518</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.965301038660109</v>
+      </c>
+      <c r="E32" t="n">
+        <v>57.67625729172973</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>7.018507393632339</v>
+      </c>
+      <c r="C33" t="n">
+        <v>7.26938859393712</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1468635160837836</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7.018507393632339</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
